--- a/dcf/FTNT.xlsx
+++ b/dcf/FTNT.xlsx
@@ -863,7 +863,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1119,25 +1119,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.07511565570057473</v>
+        <v>0.07512356114122815</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.08011565570057473</v>
+        <v>0.08012356114122815</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.08511565570057472</v>
+        <v>0.08512356114122814</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.09011565570057473</v>
+        <v>0.09012356114122815</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.09511565570057473</v>
+        <v>0.09512356114122815</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.1001156557005747</v>
+        <v>0.1001235611412281</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.1051156557005747</v>
+        <v>0.1051235611412281</v>
       </c>
     </row>
     <row r="5">
@@ -1145,25 +1145,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>49.06574457198901</v>
+        <v>49.06310226246448</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>47.4330469111289</v>
+        <v>47.43052546153152</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>45.8747975548827</v>
+        <v>45.87239071511339</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>44.3871565830886</v>
+        <v>44.38485845755363</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>42.96650134775531</v>
+        <v>42.96430637362122</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>41.60941317680835</v>
+        <v>41.60731610368684</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>40.31266495019943</v>
+        <v>40.31066082116197</v>
       </c>
     </row>
     <row r="6">
@@ -1171,25 +1171,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>51.89850575376969</v>
+        <v>51.89565515670283</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>50.13737396667205</v>
+        <v>50.13465459348794</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>48.45706683745371</v>
+        <v>48.45447187802631</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>46.85340065805956</v>
+        <v>46.85092368940411</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>45.32242898281982</v>
+        <v>45.32006394530875</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>43.86042808600622</v>
+        <v>43.85816926115088</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>42.46388337461722</v>
+        <v>42.46172536430574</v>
       </c>
     </row>
     <row r="7">
@@ -1197,25 +1197,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>54.73126693555036</v>
+        <v>54.72820805094116</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>52.84170102221519</v>
+        <v>52.83878372544437</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>51.03933612002471</v>
+        <v>51.03655304093925</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>49.3196447330305</v>
+        <v>49.31698892125458</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>47.67835661788435</v>
+        <v>47.67582151699627</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>46.11144299520407</v>
+        <v>46.10902241861492</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>44.61510179903499</v>
+        <v>44.61278990744947</v>
       </c>
     </row>
     <row r="8">
@@ -1223,25 +1223,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>57.56402811733104</v>
+        <v>57.56076094517951</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>55.54602807775832</v>
+        <v>55.54291285740077</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>53.62160540259572</v>
+        <v>53.61863420385217</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>51.78588880800146</v>
+        <v>51.78305415310506</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>50.03428425294886</v>
+        <v>50.0315790886838</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>48.36245790440194</v>
+        <v>48.35987557607896</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>46.76632022345278</v>
+        <v>46.76385445059324</v>
       </c>
     </row>
     <row r="9">
@@ -1249,25 +1249,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>60.39678929911172</v>
+        <v>60.39331383941785</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>58.25035513330148</v>
+        <v>58.24704198935718</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>56.20387468516673</v>
+        <v>56.2007153667651</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>54.25213288297241</v>
+        <v>54.24911938495553</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>52.39021188801338</v>
+        <v>52.38733666037134</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>50.61347281359981</v>
+        <v>50.61072873354301</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>48.91753864787056</v>
+        <v>48.91491899373699</v>
       </c>
     </row>
     <row r="10">
@@ -1275,25 +1275,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>63.22955048089239</v>
+        <v>63.22586673365619</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>60.95468218884461</v>
+        <v>60.9511711213136</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>58.78614396773774</v>
+        <v>58.78279652967802</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>56.71837695794336</v>
+        <v>56.71518461680599</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>54.74613952307791</v>
+        <v>54.74309423205886</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>52.86448772279767</v>
+        <v>52.86158189100704</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>51.06875707228835</v>
+        <v>51.06598353688074</v>
       </c>
     </row>
     <row r="11">
@@ -1301,25 +1301,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>66.06231166267307</v>
+        <v>66.05841962789454</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>63.65900924438775</v>
+        <v>63.65530025327002</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>61.36841325030874</v>
+        <v>61.36487769259096</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>59.1846210329143</v>
+        <v>59.18124984865648</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>57.10206715814242</v>
+        <v>57.09885180374639</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>55.11550263199554</v>
+        <v>55.11243504847109</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>53.21997549670614</v>
+        <v>53.2170480800245</v>
       </c>
     </row>
     <row r="13">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>156.25</v>
+        <v>161.6100006103516</v>
       </c>
     </row>
     <row r="14">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.09011565570057473</v>
+        <v>0.09012356114122815</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.9483712982766146</v>
+        <v>0.9483726516760821</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24456,7 +24456,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>156.25</v>
+        <v>161.6100006103516</v>
       </c>
     </row>
     <row r="49">
@@ -24618,13 +24618,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>51.78588880800146</v>
+        <v>51.78305415310506</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>70.15223997784784</v>
+        <v>70.14817045804514</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>38.14952128425249</v>
+        <v>38.14758984200124</v>
       </c>
     </row>
     <row r="59">
